--- a/data/trans_camb/P62-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P62-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 8,55</t>
+          <t>-15,84; 9,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 0,68</t>
+          <t>-24,85; -0,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-40,1; -16,13</t>
+          <t>-39,75; -15,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 22,58</t>
+          <t>2,96; 22,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 14,57</t>
+          <t>-4,49; 15,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 5,12</t>
+          <t>-12,26; 5,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 13,81</t>
+          <t>-1,97; 13,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 6,39</t>
+          <t>-8,95; 6,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-21,58; -6,44</t>
+          <t>-20,42; -6,16</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,6; 20,2</t>
+          <t>-28,24; 21,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,0; 1,57</t>
+          <t>-44,72; 0,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-72,29; -36,19</t>
+          <t>-71,19; -36,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 117,9</t>
+          <t>9,02; 114,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 75,28</t>
+          <t>-15,3; 77,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,19; 27,41</t>
+          <t>-40,13; 28,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 45,88</t>
+          <t>-4,97; 44,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,49; 21,39</t>
+          <t>-23,73; 22,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-53,52; -19,81</t>
+          <t>-53,16; -20,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,83; -6,94</t>
+          <t>-23,13; -5,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,07; -0,78</t>
+          <t>-19,01; -1,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 5,14</t>
+          <t>-15,86; 4,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 7,7</t>
+          <t>-4,63; 7,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 7,56</t>
+          <t>-5,07; 7,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,36; 20,19</t>
+          <t>8,53; 20,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 1,75</t>
+          <t>-8,36; 1,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 3,61</t>
+          <t>-6,92; 3,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,0; 13,61</t>
+          <t>1,78; 13,89</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,99; -13,34</t>
+          <t>-38,85; -11,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,85; -1,44</t>
+          <t>-31,4; -2,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,19; 9,76</t>
+          <t>-26,67; 9,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,47; 42,52</t>
+          <t>-19,29; 39,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 41,73</t>
+          <t>-21,0; 39,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,65; 106,95</t>
+          <t>33,99; 113,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,48; 5,4</t>
+          <t>-22,94; 5,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 11,16</t>
+          <t>-18,24; 10,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,79; 43,84</t>
+          <t>4,43; 42,54</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 4,54</t>
+          <t>-18,8; 3,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 5,28</t>
+          <t>-15,17; 6,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 14,0</t>
+          <t>-8,62; 14,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 9,88</t>
+          <t>-5,45; 10,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 13,57</t>
+          <t>-4,11; 12,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 16,44</t>
+          <t>1,21; 16,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 5,95</t>
+          <t>-7,06; 5,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 8,31</t>
+          <t>-3,7; 9,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 14,37</t>
+          <t>0,88; 13,95</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 8,72</t>
+          <t>-32,56; 7,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,86; 11,32</t>
+          <t>-26,16; 13,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 30,54</t>
+          <t>-14,72; 31,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 42,18</t>
+          <t>-17,64; 45,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 58,36</t>
+          <t>-12,47; 55,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,21; 70,06</t>
+          <t>3,75; 69,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,11; 17,77</t>
+          <t>-17,52; 17,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 25,32</t>
+          <t>-9,41; 28,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 43,37</t>
+          <t>1,79; 42,5</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 2,77</t>
+          <t>-17,87; 3,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-23,77; -3,4</t>
+          <t>-24,08; -3,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 15,79</t>
+          <t>-10,02; 15,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 16,11</t>
+          <t>0,48; 17,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 7,52</t>
+          <t>-7,64; 7,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,53; 17,27</t>
+          <t>1,87; 17,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 10,34</t>
+          <t>-2,68; 9,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 2,0</t>
+          <t>-10,71; 1,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 14,3</t>
+          <t>1,12; 15,79</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,5; 5,81</t>
+          <t>-30,62; 7,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-40,89; -7,73</t>
+          <t>-41,41; -8,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 34,06</t>
+          <t>-17,82; 31,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,62; 67,01</t>
+          <t>1,27; 72,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,69; 31,63</t>
+          <t>-24,34; 33,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,73; 73,43</t>
+          <t>5,78; 74,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 30,22</t>
+          <t>-6,84; 29,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-26,71; 6,6</t>
+          <t>-25,86; 6,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,33; 43,73</t>
+          <t>2,73; 49,44</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 0,31</t>
+          <t>-27,63; 0,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 12,9</t>
+          <t>-13,92; 12,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 11,59</t>
+          <t>-19,38; 11,49</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 16,31</t>
+          <t>-3,51; 16,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,56; 23,9</t>
+          <t>2,25; 22,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,76; 28,7</t>
+          <t>10,51; 27,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 7,74</t>
+          <t>-7,64; 8,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,53; 18,41</t>
+          <t>1,69; 17,38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,97; 19,22</t>
+          <t>3,63; 19,27</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-45,45; 0,64</t>
+          <t>-45,04; 1,06</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 31,52</t>
+          <t>-23,2; 27,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-30,58; 26,75</t>
+          <t>-32,94; 25,13</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 93,89</t>
+          <t>-13,08; 90,81</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,7; 139,25</t>
+          <t>8,86; 135,37</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,39; 168,71</t>
+          <t>38,91; 163,43</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-22,79; 27,16</t>
+          <t>-20,63; 30,88</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3,89; 63,7</t>
+          <t>4,22; 60,84</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>8,41; 68,92</t>
+          <t>10,01; 68,76</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 5,0</t>
+          <t>-19,1; 4,62</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 2,47</t>
+          <t>-20,3; 3,96</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 15,73</t>
+          <t>-7,14; 16,72</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 10,62</t>
+          <t>-5,21; 11,22</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 7,73</t>
+          <t>-9,57; 8,1</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,48; 18,17</t>
+          <t>2,26; 18,25</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 6,69</t>
+          <t>-7,73; 6,87</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 4,96</t>
+          <t>-9,79; 5,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,33; 16,88</t>
+          <t>2,99; 17,23</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-30,6; 10,46</t>
+          <t>-30,95; 9,29</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-34,44; 4,16</t>
+          <t>-32,27; 8,87</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 32,54</t>
+          <t>-11,5; 35,36</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 55,31</t>
+          <t>-18,78; 59,17</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-37,61; 39,86</t>
+          <t>-34,41; 40,77</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,39; 93,71</t>
+          <t>7,9; 94,53</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-18,62; 21,81</t>
+          <t>-19,4; 22,36</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-25,2; 15,46</t>
+          <t>-24,44; 16,83</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8,34; 52,7</t>
+          <t>7,45; 54,73</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-17,12; -1,81</t>
+          <t>-17,52; -2,35</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 9,27</t>
+          <t>-7,12; 9,7</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 12,98</t>
+          <t>-5,76; 13,28</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 9,15</t>
+          <t>-2,17; 9,55</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,18; 18,71</t>
+          <t>5,18; 18,98</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,97; 62,24</t>
+          <t>15,08; 61,96</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 4,22</t>
+          <t>-5,67; 4,43</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,83; 13,78</t>
+          <t>3,61; 14,25</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11,38; 48,18</t>
+          <t>11,22; 46,38</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-31,36; -3,79</t>
+          <t>-31,89; -5,16</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 19,84</t>
+          <t>-13,28; 20,75</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 28,15</t>
+          <t>-10,74; 27,56</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 39,31</t>
+          <t>-7,57; 42,54</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>17,57; 79,18</t>
+          <t>18,49; 82,05</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>55,09; 270,67</t>
+          <t>55,97; 267,2</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 12,79</t>
+          <t>-15,14; 13,31</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>9,78; 41,1</t>
+          <t>9,64; 43,28</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>31,43; 143,37</t>
+          <t>30,26; 140,91</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-21,47; -6,05</t>
+          <t>-21,66; -6,7</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-21,6; -6,44</t>
+          <t>-20,77; -5,1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 14,72</t>
+          <t>-2,65; 14,44</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 8,85</t>
+          <t>-1,55; 9,43</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,7; 13,05</t>
+          <t>2,4; 13,5</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10,54; 21,51</t>
+          <t>10,89; 21,42</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 4,03</t>
+          <t>-5,09; 4,21</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 7,22</t>
+          <t>-2,23; 7,04</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>9,94; 19,07</t>
+          <t>10,26; 19,38</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-32,51; -10,42</t>
+          <t>-33,07; -11,53</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-32,59; -11,06</t>
+          <t>-32,0; -9,02</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 26,03</t>
+          <t>-3,51; 24,85</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 41,58</t>
+          <t>-6,49; 44,24</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,16; 62,93</t>
+          <t>8,93; 63,61</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>37,6; 105,01</t>
+          <t>41,54; 104,97</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 11,91</t>
+          <t>-13,08; 12,82</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 21,07</t>
+          <t>-5,74; 20,29</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>25,05; 56,0</t>
+          <t>26,47; 57,68</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-14,1; -6,94</t>
+          <t>-13,86; -6,97</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-11,59; -4,86</t>
+          <t>-11,88; -4,67</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 3,51</t>
+          <t>-4,89; 3,51</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,89</t>
+          <t>1,76; 6,79</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,16</t>
+          <t>2,92; 8,33</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,97; 36,22</t>
+          <t>11,92; 35,15</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,3</t>
+          <t>-2,16; 2,1</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,1</t>
+          <t>-0,45; 3,74</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>8,14; 23,3</t>
+          <t>8,18; 21,92</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-25,03; -13,3</t>
+          <t>-24,7; -13,3</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-20,64; -9,42</t>
+          <t>-21,02; -8,86</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 6,66</t>
+          <t>-8,49; 6,65</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>7,01; 29,37</t>
+          <t>6,64; 29,12</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>10,56; 34,94</t>
+          <t>10,92; 35,62</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>47,7; 142,68</t>
+          <t>46,95; 147,57</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 6,69</t>
+          <t>-5,9; 6,14</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 11,75</t>
+          <t>-1,24; 10,83</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>22,51; 65,35</t>
+          <t>22,54; 60,62</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P62-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P62-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-28,13</t>
+          <t>-27,11</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,03</t>
+          <t>-5,07</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-13,58</t>
+          <t>-14,33</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 9,23</t>
+          <t>-15,32; 8,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,85; -0,09</t>
+          <t>-23,65; 1,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-39,75; -15,67</t>
+          <t>-38,32; -15,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 22,21</t>
+          <t>1,96; 21,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 15,2</t>
+          <t>-5,01; 15,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 5,26</t>
+          <t>-14,11; 2,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 13,54</t>
+          <t>-2,26; 14,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 6,78</t>
+          <t>-9,14; 6,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-20,42; -6,16</t>
+          <t>-20,77; -7,21</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-57,35%</t>
+          <t>-55,27%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-12,35%</t>
+          <t>-20,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-38,97%</t>
+          <t>-41,13%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-28,24; 21,46</t>
+          <t>-27,95; 21,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-44,72; 0,14</t>
+          <t>-42,61; 4,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-71,19; -36,49</t>
+          <t>-69,97; -36,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,02; 114,84</t>
+          <t>5,09; 107,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 77,56</t>
+          <t>-17,39; 85,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,13; 28,95</t>
+          <t>-45,32; 13,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 44,62</t>
+          <t>-5,88; 46,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,73; 22,72</t>
+          <t>-23,35; 21,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-53,16; -20,31</t>
+          <t>-54,36; -24,68</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,45</t>
+          <t>-2,86</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,09</t>
+          <t>13,22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,67</t>
+          <t>8,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,13; -5,66</t>
+          <t>-23,24; -5,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-19,01; -1,38</t>
+          <t>-18,96; -0,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 4,85</t>
+          <t>-13,01; 7,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 7,39</t>
+          <t>-5,46; 6,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 7,25</t>
+          <t>-5,17; 7,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,53; 20,81</t>
+          <t>6,62; 18,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 1,64</t>
+          <t>-9,32; 1,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 3,26</t>
+          <t>-6,98; 3,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 13,89</t>
+          <t>2,31; 13,62</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-9,8%</t>
+          <t>-5,14%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,85; -11,76</t>
+          <t>-39,0; -9,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,4; -2,54</t>
+          <t>-30,97; -1,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,67; 9,41</t>
+          <t>-21,5; 13,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 39,47</t>
+          <t>-21,68; 36,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,0; 39,54</t>
+          <t>-21,28; 37,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,99; 113,78</t>
+          <t>25,52; 103,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 5,12</t>
+          <t>-25,01; 4,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 10,28</t>
+          <t>-18,63; 11,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,43; 42,54</t>
+          <t>5,74; 43,17</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,23</t>
+          <t>1,52</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,28</t>
+          <t>9,5</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,57</t>
+          <t>7,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 3,61</t>
+          <t>-17,65; 3,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,17; 6,08</t>
+          <t>-15,18; 6,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 14,2</t>
+          <t>-9,51; 12,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 10,7</t>
+          <t>-6,28; 10,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 12,95</t>
+          <t>-4,4; 12,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 16,19</t>
+          <t>2,22; 16,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 5,51</t>
+          <t>-7,62; 5,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 9,81</t>
+          <t>-4,76; 8,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 13,95</t>
+          <t>1,06; 13,99</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 7,46</t>
+          <t>-30,61; 8,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-26,16; 13,17</t>
+          <t>-25,99; 13,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 31,23</t>
+          <t>-16,05; 26,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 45,9</t>
+          <t>-19,97; 41,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 55,71</t>
+          <t>-14,82; 52,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,75; 69,83</t>
+          <t>6,46; 71,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 17,77</t>
+          <t>-19,08; 16,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 28,07</t>
+          <t>-11,6; 26,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,79; 42,5</t>
+          <t>2,42; 42,82</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>3,92</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,98</t>
+          <t>8,48</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,03</t>
+          <t>7,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 3,46</t>
+          <t>-18,05; 3,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-24,08; -3,8</t>
+          <t>-24,04; -3,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 15,09</t>
+          <t>-8,89; 16,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 17,0</t>
+          <t>0,34; 17,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 7,81</t>
+          <t>-8,63; 7,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 17,13</t>
+          <t>0,18; 15,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 9,77</t>
+          <t>-2,51; 10,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 1,74</t>
+          <t>-10,58; 1,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 15,79</t>
+          <t>0,48; 14,49</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,62; 7,47</t>
+          <t>-31,29; 8,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,41; -8,07</t>
+          <t>-41,03; -7,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 31,74</t>
+          <t>-15,58; 35,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,27; 72,62</t>
+          <t>1,0; 73,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 33,83</t>
+          <t>-26,82; 30,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,78; 74,56</t>
+          <t>0,74; 67,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 29,92</t>
+          <t>-6,43; 32,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-25,86; 6,02</t>
+          <t>-26,64; 5,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,73; 49,44</t>
+          <t>1,19; 43,55</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-3,54</t>
+          <t>-4,08</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,26</t>
+          <t>18,36</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11,41</t>
+          <t>10,68</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 0,36</t>
+          <t>-26,33; 0,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 12,33</t>
+          <t>-14,46; 11,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,38; 11,49</t>
+          <t>-18,59; 10,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 16,01</t>
+          <t>-3,41; 17,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,25; 22,72</t>
+          <t>2,78; 23,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,51; 27,97</t>
+          <t>9,81; 27,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 8,72</t>
+          <t>-7,94; 9,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 17,38</t>
+          <t>0,21; 17,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,63; 19,27</t>
+          <t>2,49; 18,72</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-6,78%</t>
+          <t>-7,81%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-45,04; 1,06</t>
+          <t>-45,48; 1,3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 27,04</t>
+          <t>-23,76; 27,13</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-32,94; 25,13</t>
+          <t>-31,1; 24,22</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 90,81</t>
+          <t>-12,67; 105,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,86; 135,37</t>
+          <t>9,67; 136,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,91; 163,43</t>
+          <t>34,37; 168,41</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 30,88</t>
+          <t>-21,55; 33,1</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>4,22; 60,84</t>
+          <t>0,61; 60,2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>10,01; 68,76</t>
+          <t>5,57; 65,26</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>3,17</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,79</t>
+          <t>10,42</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>9,99</t>
+          <t>9,31</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-19,1; 4,62</t>
+          <t>-19,28; 5,21</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 3,96</t>
+          <t>-19,99; 4,96</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 16,72</t>
+          <t>-7,87; 14,91</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 11,22</t>
+          <t>-5,27; 10,91</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 8,1</t>
+          <t>-9,64; 7,94</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,26; 18,25</t>
+          <t>2,07; 18,32</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 6,87</t>
+          <t>-7,07; 7,12</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 5,26</t>
+          <t>-8,95; 5,66</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,99; 17,23</t>
+          <t>2,78; 16,92</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>25,97%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-30,95; 9,29</t>
+          <t>-31,67; 10,69</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-32,27; 8,87</t>
+          <t>-32,73; 9,82</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 35,36</t>
+          <t>-12,62; 31,63</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 59,17</t>
+          <t>-19,48; 57,88</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-34,41; 40,77</t>
+          <t>-34,17; 40,58</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,9; 94,53</t>
+          <t>7,21; 97,19</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 22,36</t>
+          <t>-18,05; 22,92</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 16,83</t>
+          <t>-22,51; 18,27</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7,45; 54,73</t>
+          <t>6,99; 53,39</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>6,21</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,7</t>
+          <t>16,94</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>25,7</t>
+          <t>13,92</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-17,52; -2,35</t>
+          <t>-17,65; -1,55</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 9,7</t>
+          <t>-7,95; 9,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 13,28</t>
+          <t>-3,07; 15,39</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 9,55</t>
+          <t>-2,36; 9,63</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,18; 18,98</t>
+          <t>5,82; 19,07</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,08; 61,96</t>
+          <t>10,57; 23,35</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 4,43</t>
+          <t>-5,32; 5,18</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3,61; 14,25</t>
+          <t>3,45; 14,03</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11,22; 46,38</t>
+          <t>8,47; 19,4</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>148,57%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>39,08%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-31,89; -5,16</t>
+          <t>-31,73; -3,0</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 20,75</t>
+          <t>-14,08; 19,23</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 27,56</t>
+          <t>-5,2; 33,2</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 42,54</t>
+          <t>-8,27; 42,43</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>18,49; 82,05</t>
+          <t>19,82; 82,59</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>55,97; 267,2</t>
+          <t>36,6; 102,67</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 13,31</t>
+          <t>-14,03; 15,37</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>9,64; 43,28</t>
+          <t>8,59; 42,02</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>30,26; 140,91</t>
+          <t>22,22; 59,34</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6,18</t>
+          <t>4,34</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,12</t>
+          <t>15,42</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>14,69</t>
+          <t>13,4</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-21,66; -6,7</t>
+          <t>-21,89; -6,19</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-20,77; -5,1</t>
+          <t>-20,98; -6,14</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 14,44</t>
+          <t>-4,16; 13,07</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 9,43</t>
+          <t>-1,05; 9,92</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,4; 13,5</t>
+          <t>2,06; 13,22</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10,89; 21,42</t>
+          <t>9,49; 20,53</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 4,21</t>
+          <t>-5,29; 4,21</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 7,04</t>
+          <t>-2,45; 6,91</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>10,26; 19,38</t>
+          <t>8,65; 17,67</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>36,84%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-33,07; -11,53</t>
+          <t>-33,3; -11,0</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-32,0; -9,02</t>
+          <t>-32,22; -10,71</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 24,85</t>
+          <t>-6,25; 22,16</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 44,24</t>
+          <t>-4,08; 48,02</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8,93; 63,61</t>
+          <t>6,87; 64,56</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>41,54; 104,97</t>
+          <t>35,21; 99,13</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 12,82</t>
+          <t>-13,53; 12,86</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 20,29</t>
+          <t>-6,44; 20,34</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>26,47; 57,68</t>
+          <t>22,3; 51,78</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,66</t>
+          <t>12,21</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>12,07</t>
+          <t>8,9</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-13,86; -6,97</t>
+          <t>-13,98; -7,08</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-11,88; -4,67</t>
+          <t>-11,52; -4,76</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 3,51</t>
+          <t>-3,29; 4,53</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,79</t>
+          <t>1,65; 6,94</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,92; 8,33</t>
+          <t>2,85; 8,19</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,92; 35,15</t>
+          <t>9,73; 14,76</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,1</t>
+          <t>-2,15; 2,12</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,74</t>
+          <t>-0,38; 3,74</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>8,18; 21,92</t>
+          <t>6,78; 11,0</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-0,78%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>24,99%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-24,7; -13,3</t>
+          <t>-24,68; -13,44</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-21,02; -8,86</t>
+          <t>-20,6; -9,21</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 6,65</t>
+          <t>-5,85; 8,69</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>6,64; 29,12</t>
+          <t>6,35; 29,67</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>10,92; 35,62</t>
+          <t>11,08; 35,38</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>46,95; 147,57</t>
+          <t>37,59; 64,33</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 6,14</t>
+          <t>-5,88; 6,18</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 10,83</t>
+          <t>-1,03; 10,69</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>22,54; 60,62</t>
+          <t>18,14; 31,7</t>
         </is>
       </c>
     </row>
